--- a/data/trans_orig/P04B3_3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_3_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene goteras, humedades en paredes, suelos, techos o cimientos, o podredumbre en suelos, marcos de ventanas o puertas en 2023</t>
+          <t>Población según si su vivienda tiene goteras, humedades en paredes, suelos, techos o cimientos, o podredumbre en suelos, marcos de ventanas o puertas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1797</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24734</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23731</t>
+          <t>22309</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48574</t>
+          <t>47109</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>12816</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30361</t>
+          <t>29839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41658</t>
+          <t>40928</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70597</t>
+          <t>69459</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>448424</t>
+          <t>451126</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>476116</t>
+          <t>478002</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>407279</t>
+          <t>408502</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>425928</t>
+          <t>427070</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>865071</t>
+          <t>864621</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>897076</t>
+          <t>898070</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>902</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22721</t>
+          <t>22719</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45226</t>
+          <t>45587</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>14037</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29488</t>
+          <t>29632</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>40597</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>70124</t>
+          <t>67064</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>406311</t>
+          <t>406125</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>428913</t>
+          <t>428746</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>349976</t>
+          <t>350279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>365696</t>
+          <t>366180</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>762242</t>
+          <t>765338</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>791225</t>
+          <t>790789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,73%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19964</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>913</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19381</t>
+          <t>19686</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9736</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47493</t>
+          <t>48548</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>10837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22803</t>
+          <t>22954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66537</t>
+          <t>67968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>603401</t>
+          <t>601898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>654707</t>
+          <t>654425</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>143954</t>
+          <t>144021</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156285</t>
+          <t>155968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>753055</t>
+          <t>751304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>815206</t>
+          <t>811223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19746</t>
+          <t>20128</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>17949</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13128</t>
+          <t>14071</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31896</t>
+          <t>32666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62441</t>
+          <t>60658</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98980</t>
+          <t>99316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75942</t>
+          <t>73881</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>626196</t>
+          <t>621809</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>346571</t>
+          <t>346572</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150815</t>
+          <t>151170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>882823</t>
+          <t>829425</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>923516</t>
+          <t>923029</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>962011</t>
+          <t>964470</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>344785</t>
+          <t>355427</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>887193</t>
+          <t>890163</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1116427</t>
+          <t>1167212</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1837218</t>
+          <t>1835271</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2012015</t>
+          <t>2012016</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2012015</t>
+          <t>2012016</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2012015</t>
+          <t>2012016</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29456</t>
+          <t>27769</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42090</t>
+          <t>44964</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27429</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63945</t>
+          <t>57658</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50369</t>
+          <t>50718</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84898</t>
+          <t>83847</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63804</t>
+          <t>64261</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>104721</t>
+          <t>106807</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>121366</t>
+          <t>119068</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>178548</t>
+          <t>176048</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>371917</t>
+          <t>371927</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>409165</t>
+          <t>408556</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>712935</t>
+          <t>708527</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>764222</t>
+          <t>762366</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1094850</t>
+          <t>1096984</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1161748</t>
+          <t>1163044</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23202</t>
+          <t>22205</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15990</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27919</t>
+          <t>27028</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22448</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57474</t>
+          <t>55930</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85311</t>
+          <t>84722</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62609</t>
+          <t>63312</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>96508</t>
+          <t>98065</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>208825</t>
+          <t>209604</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>234939</t>
+          <t>235680</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>665568</t>
+          <t>667057</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>695563</t>
+          <t>696692</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>888049</t>
+          <t>886461</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>925855</t>
+          <t>926248</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70728</t>
+          <t>70821</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,47 +3481,47 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>51591</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>38470</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>71744</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>51591</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>37542</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>71622</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>81676</t>
+          <t>80252</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>130320</t>
+          <t>129316</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>187280</t>
+          <t>190435</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>282535</t>
+          <t>283478</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>284950</t>
+          <t>280246</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1065731</t>
+          <t>1066428</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>518341</t>
+          <t>519076</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1299876</t>
+          <t>1364438</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3035165</t>
+          <t>3038071</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3145773</t>
+          <t>3143186</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2465411</t>
+          <t>2461914</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3235801</t>
+          <t>3239536</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5547953</t>
+          <t>5489613</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6328487</t>
+          <t>6329185</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,07%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_3_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>18769</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>13826</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24221</t>
+          <t>27633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33435</t>
+          <t>37625</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22309</t>
+          <t>26783</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47109</t>
+          <t>54097</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20196</t>
+          <t>24917</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12816</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29839</t>
+          <t>35598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>53631</t>
+          <t>62543</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40928</t>
+          <t>47837</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69459</t>
+          <t>81582</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>465486</t>
+          <t>505309</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>451126</t>
+          <t>489039</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>478002</t>
+          <t>518204</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>418394</t>
+          <t>454234</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>408502</t>
+          <t>441509</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>427070</t>
+          <t>463091</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>883880</t>
+          <t>959543</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>864621</t>
+          <t>938308</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>898070</t>
+          <t>975361</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>446125</t>
+          <t>486979</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>951337</t>
+          <t>1037597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>868</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,67 +1216,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>5124</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2199</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>10672</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>0,24%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3311</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1272</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6990</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31839</t>
+          <t>34403</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>24724</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45587</t>
+          <t>46812</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20447</t>
+          <t>23323</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>16040</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29632</t>
+          <t>33771</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>52286</t>
+          <t>57726</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>41263</t>
+          <t>44547</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>67064</t>
+          <t>72616</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>419655</t>
+          <t>447941</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>406125</t>
+          <t>435432</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>428746</t>
+          <t>458173</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>359541</t>
+          <t>395564</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>350279</t>
+          <t>385383</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>366180</t>
+          <t>403724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>779196</t>
+          <t>843505</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>765338</t>
+          <t>826811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>790789</t>
+          <t>856766</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>11136</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>680</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19686</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27904</t>
+          <t>30448</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48548</t>
+          <t>41503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15859</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>11643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22954</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>43764</t>
+          <t>48154</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>36420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67968</t>
+          <t>62648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>629292</t>
+          <t>429093</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>601898</t>
+          <t>416914</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>654425</t>
+          <t>440679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>150891</t>
+          <t>169111</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>144021</t>
+          <t>161648</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155968</t>
+          <t>175171</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>780182</t>
+          <t>598205</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>751304</t>
+          <t>581923</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>811223</t>
+          <t>611112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>667259</t>
+          <t>470677</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>834170</t>
+          <t>658175</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>834170</t>
+          <t>658175</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>834170</t>
+          <t>658175</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20128</t>
+          <t>22195</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>7852</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17949</t>
+          <t>19436</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22284</t>
+          <t>25799</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14071</t>
+          <t>17855</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32666</t>
+          <t>37659</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>78222</t>
+          <t>87865</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60658</t>
+          <t>69329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>99316</t>
+          <t>107253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>268349</t>
+          <t>73136</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73881</t>
+          <t>59497</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>621809</t>
+          <t>90258</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>346572</t>
+          <t>161001</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151170</t>
+          <t>138165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>829425</t>
+          <t>187756</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>945434</t>
+          <t>1030640</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>923029</t>
+          <t>1010005</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>964470</t>
+          <t>1050582</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>697726</t>
+          <t>773942</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>355427</t>
+          <t>755668</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>890163</t>
+          <t>788323</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1643160</t>
+          <t>1804582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1167212</t>
+          <t>1776820</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1835271</t>
+          <t>1828059</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,8%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>859539</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>859539</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>977197</t>
+          <t>859539</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1991382</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1991382</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2012016</t>
+          <t>1991382</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>22141</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>13693</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27769</t>
+          <t>33322</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20918</t>
+          <t>20733</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>29535</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>38955</t>
+          <t>42874</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26342</t>
+          <t>31720</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>57658</t>
+          <t>56825</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>64582</t>
+          <t>80624</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50718</t>
+          <t>65254</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83847</t>
+          <t>101014</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>86061</t>
+          <t>98723</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64261</t>
+          <t>83455</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>106807</t>
+          <t>118427</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>150643</t>
+          <t>179347</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>119068</t>
+          <t>157531</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>176048</t>
+          <t>204469</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>392427</t>
+          <t>465199</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>371927</t>
+          <t>444063</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>408556</t>
+          <t>482864</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>734356</t>
+          <t>711394</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>708527</t>
+          <t>691567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>762366</t>
+          <t>727505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1126783</t>
+          <t>1176594</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1096984</t>
+          <t>1148938</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1163044</t>
+          <t>1200636</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22205</t>
+          <t>15015</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>17593</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>27028</t>
+          <t>28393</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>27528</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>69446</t>
+          <t>81527</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>55930</t>
+          <t>64563</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>84722</t>
+          <t>98728</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>78199</t>
+          <t>93019</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63312</t>
+          <t>75843</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>98065</t>
+          <t>114739</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>226934</t>
+          <t>221616</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>209604</t>
+          <t>203918</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>235680</t>
+          <t>230542</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>682084</t>
+          <t>751914</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>667057</t>
+          <t>734684</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>696692</t>
+          <t>769845</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>909019</t>
+          <t>973529</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>886461</t>
+          <t>948868</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>926248</t>
+          <t>991542</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>760795</t>
+          <t>843684</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>760795</t>
+          <t>843684</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>760795</t>
+          <t>843684</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1001303</t>
+          <t>1080912</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1001303</t>
+          <t>1080912</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1001303</t>
+          <t>1080912</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>51094</t>
+          <t>59286</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34629</t>
+          <t>43565</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70821</t>
+          <t>77946</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>51591</t>
+          <t>56202</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>44618</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71744</t>
+          <t>72182</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>102686</t>
+          <t>115488</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>80252</t>
+          <t>95388</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>129316</t>
+          <t>137789</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>244735</t>
+          <t>282458</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>190435</t>
+          <t>248498</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>283478</t>
+          <t>320849</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>480358</t>
+          <t>319332</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>280246</t>
+          <t>286769</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1066428</t>
+          <t>350997</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>725094</t>
+          <t>601790</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>519076</t>
+          <t>558109</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1364438</t>
+          <t>647581</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3079226</t>
+          <t>3099798</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3038071</t>
+          <t>3052307</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3143186</t>
+          <t>3136361</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3042993</t>
+          <t>3256159</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2461914</t>
+          <t>3222639</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3239536</t>
+          <t>3288936</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6122220</t>
+          <t>6355956</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5489613</t>
+          <t>6306057</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6329185</t>
+          <t>6403668</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3375056</t>
+          <t>3441542</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3375056</t>
+          <t>3441542</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3375056</t>
+          <t>3441542</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3574943</t>
+          <t>3631692</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3574943</t>
+          <t>3631692</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3574943</t>
+          <t>3631692</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6949999</t>
+          <t>7073234</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6949999</t>
+          <t>7073234</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6949999</t>
+          <t>7073234</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
